--- a/Location Table.xlsx
+++ b/Location Table.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Uber Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data Analyst Data\Uber Trip Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F184BB6-6751-4A07-86F9-39859107F99E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EA6947B-05A5-4B01-8711-4A5ACC4BD4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13152" xr2:uid="{7782159F-C812-418D-AB4A-8CD7B155F1AF}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7782159F-C812-418D-AB4A-8CD7B155F1AF}"/>
   </bookViews>
   <sheets>
     <sheet name="Location Table" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Location Table'!$A$1:$C$266</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1683,14 +1686,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99AA6205-80AD-4651-9359-C03FF8934890}">
   <dimension ref="A1:C266"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.625" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.69921875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1701,7 +1704,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1712,7 +1715,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1723,7 +1726,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1734,7 +1737,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1745,7 +1748,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1756,7 +1759,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1767,7 +1770,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1778,7 +1781,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1789,7 +1792,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1800,7 +1803,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1811,7 +1814,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1822,7 +1825,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1833,7 +1836,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1855,7 +1858,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1866,7 +1869,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1877,7 +1880,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1888,7 +1891,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1899,7 +1902,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1910,7 +1913,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1921,7 +1924,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1932,7 +1935,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1943,7 +1946,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1954,7 +1957,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1965,7 +1968,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1976,7 +1979,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1987,7 +1990,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1998,7 +2001,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2009,7 +2012,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -2020,7 +2023,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -2031,7 +2034,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -2042,7 +2045,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -2053,7 +2056,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -2064,7 +2067,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -2075,7 +2078,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -2086,7 +2089,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -2097,7 +2100,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -2108,7 +2111,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -2119,7 +2122,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -2141,7 +2144,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -2152,7 +2155,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -2163,7 +2166,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -2174,7 +2177,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -2185,7 +2188,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -2196,7 +2199,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -2207,7 +2210,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -2218,7 +2221,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -2229,7 +2232,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -2240,7 +2243,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -2251,7 +2254,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -2262,7 +2265,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2284,7 +2287,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2295,7 +2298,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2306,7 +2309,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2317,7 +2320,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2328,7 +2331,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2339,7 +2342,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2350,7 +2353,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2361,7 +2364,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2372,7 +2375,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2383,7 +2386,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2394,7 +2397,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2405,7 +2408,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2416,7 +2419,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
@@ -2427,7 +2430,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>67</v>
       </c>
@@ -2438,7 +2441,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>68</v>
       </c>
@@ -2449,7 +2452,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>69</v>
       </c>
@@ -2460,7 +2463,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>70</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>71</v>
       </c>
@@ -2482,7 +2485,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>72</v>
       </c>
@@ -2493,7 +2496,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>73</v>
       </c>
@@ -2504,7 +2507,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>74</v>
       </c>
@@ -2515,7 +2518,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>75</v>
       </c>
@@ -2526,7 +2529,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>76</v>
       </c>
@@ -2537,7 +2540,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>77</v>
       </c>
@@ -2548,7 +2551,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>78</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>79</v>
       </c>
@@ -2570,7 +2573,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>80</v>
       </c>
@@ -2581,7 +2584,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>81</v>
       </c>
@@ -2592,7 +2595,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>82</v>
       </c>
@@ -2603,7 +2606,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>83</v>
       </c>
@@ -2614,7 +2617,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>84</v>
       </c>
@@ -2625,7 +2628,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>85</v>
       </c>
@@ -2636,7 +2639,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>86</v>
       </c>
@@ -2647,7 +2650,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>87</v>
       </c>
@@ -2658,7 +2661,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>88</v>
       </c>
@@ -2669,7 +2672,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>89</v>
       </c>
@@ -2680,7 +2683,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>90</v>
       </c>
@@ -2691,7 +2694,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>91</v>
       </c>
@@ -2702,7 +2705,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>92</v>
       </c>
@@ -2713,7 +2716,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>93</v>
       </c>
@@ -2724,7 +2727,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>94</v>
       </c>
@@ -2735,7 +2738,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>95</v>
       </c>
@@ -2746,7 +2749,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>96</v>
       </c>
@@ -2757,7 +2760,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>97</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>98</v>
       </c>
@@ -2779,7 +2782,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>99</v>
       </c>
@@ -2790,7 +2793,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>100</v>
       </c>
@@ -2801,7 +2804,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>101</v>
       </c>
@@ -2812,7 +2815,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>102</v>
       </c>
@@ -2823,7 +2826,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>103</v>
       </c>
@@ -2834,7 +2837,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>104</v>
       </c>
@@ -2845,7 +2848,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>105</v>
       </c>
@@ -2856,7 +2859,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>106</v>
       </c>
@@ -2867,7 +2870,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>107</v>
       </c>
@@ -2878,7 +2881,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>108</v>
       </c>
@@ -2889,7 +2892,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>109</v>
       </c>
@@ -2900,7 +2903,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>110</v>
       </c>
@@ -2911,7 +2914,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>111</v>
       </c>
@@ -2922,7 +2925,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>112</v>
       </c>
@@ -2933,7 +2936,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>113</v>
       </c>
@@ -2944,7 +2947,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>114</v>
       </c>
@@ -2955,7 +2958,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>115</v>
       </c>
@@ -2966,7 +2969,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>116</v>
       </c>
@@ -2977,7 +2980,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>117</v>
       </c>
@@ -2988,7 +2991,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>118</v>
       </c>
@@ -2999,7 +3002,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>119</v>
       </c>
@@ -3010,7 +3013,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>120</v>
       </c>
@@ -3021,7 +3024,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>121</v>
       </c>
@@ -3032,7 +3035,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>122</v>
       </c>
@@ -3043,7 +3046,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>123</v>
       </c>
@@ -3054,7 +3057,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>124</v>
       </c>
@@ -3065,7 +3068,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>125</v>
       </c>
@@ -3076,7 +3079,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>126</v>
       </c>
@@ -3087,7 +3090,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>127</v>
       </c>
@@ -3098,7 +3101,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>128</v>
       </c>
@@ -3109,7 +3112,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>129</v>
       </c>
@@ -3120,7 +3123,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>130</v>
       </c>
@@ -3131,7 +3134,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>131</v>
       </c>
@@ -3142,7 +3145,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>132</v>
       </c>
@@ -3153,7 +3156,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>133</v>
       </c>
@@ -3164,7 +3167,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>134</v>
       </c>
@@ -3175,7 +3178,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>135</v>
       </c>
@@ -3186,7 +3189,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>136</v>
       </c>
@@ -3197,7 +3200,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>137</v>
       </c>
@@ -3208,7 +3211,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>138</v>
       </c>
@@ -3219,7 +3222,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>139</v>
       </c>
@@ -3230,7 +3233,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>140</v>
       </c>
@@ -3241,7 +3244,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>141</v>
       </c>
@@ -3252,7 +3255,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>142</v>
       </c>
@@ -3263,7 +3266,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>143</v>
       </c>
@@ -3274,7 +3277,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>144</v>
       </c>
@@ -3285,7 +3288,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>145</v>
       </c>
@@ -3296,7 +3299,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>146</v>
       </c>
@@ -3307,7 +3310,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>147</v>
       </c>
@@ -3318,7 +3321,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>148</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>149</v>
       </c>
@@ -3340,7 +3343,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>150</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>151</v>
       </c>
@@ -3362,7 +3365,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>152</v>
       </c>
@@ -3373,7 +3376,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>153</v>
       </c>
@@ -3384,7 +3387,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>154</v>
       </c>
@@ -3395,7 +3398,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>155</v>
       </c>
@@ -3406,7 +3409,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>156</v>
       </c>
@@ -3417,7 +3420,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>157</v>
       </c>
@@ -3428,7 +3431,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>158</v>
       </c>
@@ -3439,7 +3442,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>159</v>
       </c>
@@ -3450,7 +3453,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>160</v>
       </c>
@@ -3461,7 +3464,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>161</v>
       </c>
@@ -3472,7 +3475,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>162</v>
       </c>
@@ -3483,7 +3486,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>163</v>
       </c>
@@ -3494,7 +3497,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>164</v>
       </c>
@@ -3505,7 +3508,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>165</v>
       </c>
@@ -3516,7 +3519,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>166</v>
       </c>
@@ -3527,7 +3530,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>167</v>
       </c>
@@ -3538,7 +3541,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>168</v>
       </c>
@@ -3549,7 +3552,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>169</v>
       </c>
@@ -3560,7 +3563,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>170</v>
       </c>
@@ -3571,7 +3574,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>171</v>
       </c>
@@ -3582,7 +3585,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>172</v>
       </c>
@@ -3593,7 +3596,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>173</v>
       </c>
@@ -3604,7 +3607,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>174</v>
       </c>
@@ -3615,7 +3618,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>175</v>
       </c>
@@ -3626,7 +3629,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>176</v>
       </c>
@@ -3637,7 +3640,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>177</v>
       </c>
@@ -3648,7 +3651,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>178</v>
       </c>
@@ -3659,7 +3662,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>179</v>
       </c>
@@ -3670,7 +3673,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>180</v>
       </c>
@@ -3681,7 +3684,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>181</v>
       </c>
@@ -3692,7 +3695,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>182</v>
       </c>
@@ -3703,7 +3706,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>183</v>
       </c>
@@ -3714,7 +3717,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>184</v>
       </c>
@@ -3725,7 +3728,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>185</v>
       </c>
@@ -3736,7 +3739,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>186</v>
       </c>
@@ -3747,7 +3750,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>187</v>
       </c>
@@ -3758,7 +3761,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>188</v>
       </c>
@@ -3769,7 +3772,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>189</v>
       </c>
@@ -3780,7 +3783,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>190</v>
       </c>
@@ -3791,7 +3794,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>191</v>
       </c>
@@ -3802,7 +3805,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>192</v>
       </c>
@@ -3813,7 +3816,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>193</v>
       </c>
@@ -3824,7 +3827,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>194</v>
       </c>
@@ -3835,7 +3838,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>195</v>
       </c>
@@ -3846,7 +3849,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>196</v>
       </c>
@@ -3857,7 +3860,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>197</v>
       </c>
@@ -3868,7 +3871,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>198</v>
       </c>
@@ -3879,7 +3882,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>199</v>
       </c>
@@ -3890,7 +3893,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>200</v>
       </c>
@@ -3901,7 +3904,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>201</v>
       </c>
@@ -3912,7 +3915,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>202</v>
       </c>
@@ -3923,7 +3926,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>203</v>
       </c>
@@ -3934,7 +3937,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>204</v>
       </c>
@@ -3945,7 +3948,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>205</v>
       </c>
@@ -3956,7 +3959,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>206</v>
       </c>
@@ -3967,7 +3970,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>207</v>
       </c>
@@ -3978,7 +3981,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>208</v>
       </c>
@@ -3989,7 +3992,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>209</v>
       </c>
@@ -4000,7 +4003,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>210</v>
       </c>
@@ -4011,7 +4014,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>211</v>
       </c>
@@ -4022,7 +4025,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>212</v>
       </c>
@@ -4033,7 +4036,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>213</v>
       </c>
@@ -4044,7 +4047,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>214</v>
       </c>
@@ -4055,7 +4058,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>215</v>
       </c>
@@ -4066,7 +4069,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>216</v>
       </c>
@@ -4077,7 +4080,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>217</v>
       </c>
@@ -4088,7 +4091,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>218</v>
       </c>
@@ -4099,7 +4102,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>219</v>
       </c>
@@ -4110,7 +4113,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>220</v>
       </c>
@@ -4121,7 +4124,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>221</v>
       </c>
@@ -4132,7 +4135,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>222</v>
       </c>
@@ -4143,7 +4146,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>223</v>
       </c>
@@ -4154,7 +4157,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>224</v>
       </c>
@@ -4165,7 +4168,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>225</v>
       </c>
@@ -4176,7 +4179,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>226</v>
       </c>
@@ -4187,7 +4190,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>227</v>
       </c>
@@ -4198,7 +4201,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>228</v>
       </c>
@@ -4209,7 +4212,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>229</v>
       </c>
@@ -4220,7 +4223,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>230</v>
       </c>
@@ -4231,7 +4234,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>231</v>
       </c>
@@ -4242,7 +4245,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>232</v>
       </c>
@@ -4253,7 +4256,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>233</v>
       </c>
@@ -4264,7 +4267,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>234</v>
       </c>
@@ -4275,7 +4278,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>235</v>
       </c>
@@ -4286,7 +4289,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>236</v>
       </c>
@@ -4297,7 +4300,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>237</v>
       </c>
@@ -4308,7 +4311,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>238</v>
       </c>
@@ -4319,7 +4322,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>239</v>
       </c>
@@ -4330,7 +4333,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>240</v>
       </c>
@@ -4341,7 +4344,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>241</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>242</v>
       </c>
@@ -4363,7 +4366,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>243</v>
       </c>
@@ -4374,7 +4377,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>244</v>
       </c>
@@ -4385,7 +4388,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>245</v>
       </c>
@@ -4396,7 +4399,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>246</v>
       </c>
@@ -4407,7 +4410,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>247</v>
       </c>
@@ -4418,7 +4421,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>248</v>
       </c>
@@ -4429,7 +4432,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>249</v>
       </c>
@@ -4440,7 +4443,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>250</v>
       </c>
@@ -4451,7 +4454,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>251</v>
       </c>
@@ -4462,7 +4465,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>252</v>
       </c>
@@ -4473,7 +4476,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>253</v>
       </c>
@@ -4484,7 +4487,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>254</v>
       </c>
@@ -4495,7 +4498,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>255</v>
       </c>
@@ -4506,7 +4509,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>256</v>
       </c>
@@ -4517,7 +4520,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>257</v>
       </c>
@@ -4528,7 +4531,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>258</v>
       </c>
@@ -4539,7 +4542,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>259</v>
       </c>
@@ -4550,7 +4553,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>260</v>
       </c>
@@ -4561,7 +4564,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>261</v>
       </c>
@@ -4572,7 +4575,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>262</v>
       </c>
@@ -4583,7 +4586,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>263</v>
       </c>
@@ -4594,7 +4597,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>264</v>
       </c>
@@ -4605,7 +4608,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>265</v>
       </c>
